--- a/guide-demarrage/ig/cm-v3-administrative-gender.xlsx
+++ b/guide-demarrage/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-26T14:21:50+00:00</t>
+    <t>2026-03-27T11:09:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/guide-demarrage/ig/cm-v3-administrative-gender.xlsx
+++ b/guide-demarrage/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T11:09:16+00:00</t>
+    <t>2026-03-27T11:14:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/guide-demarrage/ig/cm-v3-administrative-gender.xlsx
+++ b/guide-demarrage/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T11:14:29+00:00</t>
+    <t>2026-03-27T13:14:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/guide-demarrage/ig/cm-v3-administrative-gender.xlsx
+++ b/guide-demarrage/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T13:14:22+00:00</t>
+    <t>2026-03-27T14:10:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
